--- a/artfynd/A 46165-2024 artfynd.xlsx
+++ b/artfynd/A 46165-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80050709</v>
+        <v>84313544</v>
       </c>
       <c r="B2" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5449</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gaterudsfjällen, Dls</t>
+          <t>S Kuvetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>354750.6017968364</v>
+        <v>355288</v>
       </c>
       <c r="R2" t="n">
-        <v>6564888.359993952</v>
+        <v>6565399</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-06-25</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-04-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-06-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-04-09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,27 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Fredrik Wilde</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>84313575</v>
+        <v>84313425</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,37 +788,45 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>SV Kuvetjärnet, Dls</t>
+          <t>S Kuvetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>355123.5652777266</v>
+        <v>355377</v>
       </c>
       <c r="R3" t="n">
-        <v>6565227.405147197</v>
+        <v>6565311</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,19 +856,14 @@
           <t>2020-04-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-04-09</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>I gammal hänglavrik gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>84313684</v>
+        <v>84313635</v>
       </c>
       <c r="B4" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,26 +902,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6426</v>
+        <v>210</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -950,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>354804.4999040535</v>
+        <v>354834</v>
       </c>
       <c r="R4" t="n">
-        <v>6565076.010943948</v>
+        <v>6565182</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,19 +971,9 @@
           <t>2020-04-09</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-04-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,15 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>84313479</v>
+        <v>84313575</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1062,14 +1035,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>S Kuvetjärnet, Dls</t>
+          <t>SV Kuvetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>355365.721048033</v>
+        <v>355124</v>
       </c>
       <c r="R5" t="n">
-        <v>6565342.264159271</v>
+        <v>6565227</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,19 +1072,9 @@
           <t>2020-04-09</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-04-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,15 +1102,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>84313494</v>
+        <v>88763543</v>
       </c>
       <c r="B6" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,37 +1113,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6426</v>
+        <v>2810</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>S Kuvetjärnet, Dls</t>
+          <t>Gaterudsfjällen, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>355366.8634167182</v>
+        <v>355113</v>
       </c>
       <c r="R6" t="n">
-        <v>6565345.296749939</v>
+        <v>6565264</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,22 +1171,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-04-09</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-04-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,53 +1204,56 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>84313670</v>
+        <v>88763550</v>
       </c>
       <c r="B7" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6426</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>S Hålmyren, Dls</t>
+          <t>Gaterudsfjällen, Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>354822.252160466</v>
+        <v>355148</v>
       </c>
       <c r="R7" t="n">
-        <v>6565177.87422983</v>
+        <v>6565242</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,22 +1280,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-04-09</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-04-09</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,15 +1313,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>84313451</v>
+        <v>88504262</v>
       </c>
       <c r="B8" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,37 +1324,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6426</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>S Kuvetjärnet, Dls</t>
+          <t>S Trinnemyr, Gaterudsfjällen, Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>355364.6175800734</v>
+        <v>354740</v>
       </c>
       <c r="R8" t="n">
-        <v>6565340.255421336</v>
+        <v>6564799</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,22 +1378,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2020-04-09</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-04-14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2020-04-09</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-04-14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,81 +1392,66 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Wilde</t>
+          <t>Anders Boström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>84313635</v>
+        <v>84313479</v>
       </c>
       <c r="B9" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>210</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>S Hålmyren, Dls</t>
+          <t>S Kuvetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>354834.2235194158</v>
+        <v>355366</v>
       </c>
       <c r="R9" t="n">
-        <v>6565182.031954298</v>
+        <v>6565342</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1572,19 +1481,9 @@
           <t>2020-04-09</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2020-04-09</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1612,48 +1511,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>88763534</v>
+        <v>88763757</v>
       </c>
       <c r="B10" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1661,10 +1549,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>355127.720838675</v>
+        <v>354703</v>
       </c>
       <c r="R10" t="n">
-        <v>6565282.616513512</v>
+        <v>6565156</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1694,19 +1582,9 @@
           <t>2020-10-27</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2020-10-27</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1734,37 +1612,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>88763753</v>
+        <v>84313451</v>
       </c>
       <c r="B11" t="n">
-        <v>73678</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6439</v>
+        <v>6426</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1773,14 +1646,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gaterudsfjällen, Dls</t>
+          <t>S Kuvetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>354674.2941610256</v>
+        <v>355365</v>
       </c>
       <c r="R11" t="n">
-        <v>6565015.351795158</v>
+        <v>6565340</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1807,22 +1680,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2020-10-27</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-04-09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2020-10-27</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-04-09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1850,19 +1713,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>88763573</v>
+        <v>84313494</v>
       </c>
       <c r="B12" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1889,14 +1747,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gaterudsfjällen, Dls</t>
+          <t>S Kuvetjärnet, Dls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>354850.5824765097</v>
+        <v>355367</v>
       </c>
       <c r="R12" t="n">
-        <v>6564870.190364014</v>
+        <v>6565345</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1923,22 +1781,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2020-10-27</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-04-09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2020-10-27</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-04-09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1966,61 +1814,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>88763550</v>
+        <v>84313670</v>
       </c>
       <c r="B13" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6426</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gaterudsfjällen, Dls</t>
+          <t>S Hålmyren, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>355148.2535157495</v>
+        <v>354822</v>
       </c>
       <c r="R13" t="n">
-        <v>6565241.846143792</v>
+        <v>6565178</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2047,22 +1882,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2020-10-27</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-04-09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2020-10-27</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-04-09</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2090,15 +1915,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>88763757</v>
+        <v>84313684</v>
       </c>
       <c r="B14" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2106,21 +1926,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6426</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2129,14 +1949,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gaterudsfjällen, Dls</t>
+          <t>S Hålmyren, Dls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>354703.2990959955</v>
+        <v>354804</v>
       </c>
       <c r="R14" t="n">
-        <v>6565156.264957615</v>
+        <v>6565076</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2163,22 +1983,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2020-10-27</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-04-09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2020-10-27</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-04-09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2203,6 +2013,517 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>88763573</v>
+      </c>
+      <c r="B15" t="n">
+        <v>75428</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Gaterudsfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>354851</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6564870</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Säffle</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Svanskog</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2020-10-27</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2020-10-27</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>88763706</v>
+      </c>
+      <c r="B16" t="n">
+        <v>75300</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Gaterudsfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>354831</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6564916</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Säffle</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Svanskog</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2020-10-27</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2020-10-27</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>88763753</v>
+      </c>
+      <c r="B17" t="n">
+        <v>83290</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Gaterudsfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>354674</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6565015</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Säffle</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Svanskog</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2020-10-27</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2020-10-27</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>88763764</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Gaterudsfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>354712</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6565220</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Säffle</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Svanskog</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2020-10-27</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2020-10-27</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>88763534</v>
+      </c>
+      <c r="B19" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Gaterudsfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>355128</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6565283</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Säffle</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Svanskog</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2020-10-27</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2020-10-27</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Fredrik Wilde</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 46165-2024 artfynd.xlsx
+++ b/artfynd/A 46165-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88504262</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88763573</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,6 +986,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88763706</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1073,6 +1093,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84313544</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84313425</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1297,6 +1327,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84313635</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1398,6 +1433,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84313575</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1500,6 +1540,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88763543</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1609,6 +1654,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88763550</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1710,6 +1760,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84313479</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1811,6 +1866,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88763757</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1912,6 +1972,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84313451</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2013,6 +2078,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84313494</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2114,6 +2184,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84313670</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2215,6 +2290,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84313684</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2316,6 +2396,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88763753</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2417,6 +2502,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88763764</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2524,8 +2614,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88763534</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>